--- a/События стратегического наблюдения.xlsx
+++ b/События стратегического наблюдения.xlsx
@@ -1,6 +1,26 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20386"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411787B5-993E-4BC3-A4CF-943B4FA2DEF4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Справочник_типов_событий" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>тип события</t>
   </si>
@@ -234,231 +254,6 @@
   </si>
   <si>
     <t>урезание ИТ-подрядов крупным клиентом</t>
-  </si>
-  <si>
-    <t>дата события</t>
-  </si>
-  <si>
-    <t>компания или объект</t>
-  </si>
-  <si>
-    <t>краткое описание</t>
-  </si>
-  <si>
-    <t>источник</t>
-  </si>
-  <si>
-    <t>ссылка</t>
-  </si>
-  <si>
-    <t>шум или общий сдвиг</t>
-  </si>
-  <si>
-    <t>включено в выпуск</t>
-  </si>
-  <si>
-    <t>комментарий</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>США и мировая торговля</t>
-  </si>
-  <si>
-    <t>Новый виток тарифной конфронтации усилил глобальную неопределенность и давление на цепочки поставок.</t>
-  </si>
-  <si>
-    <t>AP / Business and Finance</t>
-  </si>
-  <si>
-    <t>https://www.ap.org/content/topics/business-and-finance/</t>
-  </si>
-  <si>
-    <t>мировая экономика, рынок труда, логика отрасли</t>
-  </si>
-  <si>
-    <t>тарифы и торговые риски -&gt; осторожность бизнеса -&gt; более жесткие бюджеты и найм</t>
-  </si>
-  <si>
-    <t>общий сдвиг</t>
-  </si>
-  <si>
-    <t>Использовано как часть внешнего контура 2025 года</t>
-  </si>
-  <si>
-    <t>2025-06-13</t>
-  </si>
-  <si>
-    <t>Ближний Восток и нефтяной рынок</t>
-  </si>
-  <si>
-    <t>Геополитическая эскалация и напряжение вокруг нефтяного рынка усиливали волатильность внешнего фона.</t>
-  </si>
-  <si>
-    <t>мировая экономика, экономика России</t>
-  </si>
-  <si>
-    <t>сырьевой и геополитический риск -&gt; бюджет, курс, стоимость денег -&gt; кадровая осторожность</t>
-  </si>
-  <si>
-    <t>Использовано как часть связки внешних драйверов года</t>
-  </si>
-  <si>
-    <t>2025-01-08</t>
-  </si>
-  <si>
-    <t>Глобальный рынок труда и ИИ</t>
-  </si>
-  <si>
-    <t>Глобальный контур 2025 года усилил связку между ИИ, автоматизацией, спросом на навыки и риском перераспределения офисного труда.</t>
-  </si>
-  <si>
-    <t>WEF / Future of Jobs</t>
-  </si>
-  <si>
-    <t>https://www.weforum.org/publications/series/future-of-jobs/</t>
-  </si>
-  <si>
-    <t>ИТ-рынок, рынок труда, логика отрасли</t>
-  </si>
-  <si>
-    <t>рост ИИ и автоматизации -&gt; переоценка ролей и навыков -&gt; более избирательный ИТ-найм</t>
-  </si>
-  <si>
-    <t>Использовано в стратегических сигналах периода</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>Мировой технологический сектор</t>
-  </si>
-  <si>
-    <t>В течение 2025 года мировой техсектор сохранял инвестиции в ИИ и инфраструктуру, но параллельно проходил через волны увольнений и ужесточение требований к эффективности.</t>
-  </si>
-  <si>
-    <t>Layoffs.fyi</t>
-  </si>
-  <si>
-    <t>https://layoffs.fyi/</t>
-  </si>
-  <si>
-    <t>ИТ-рынок, крупные работодатели, логика отрасли</t>
-  </si>
-  <si>
-    <t>капвложения в ИИ + давление на эффективность -&gt; увольнения и более строгий отбор ролей</t>
-  </si>
-  <si>
-    <t>Использовано как внешний ИТ-сигнал для российского рынка</t>
-  </si>
-  <si>
-    <t>2025-07-30</t>
-  </si>
-  <si>
-    <t>Резкое ухудшение финансового результата РЖД усиливало риск более осторожных инвестиций и спроса на подряд.</t>
-  </si>
-  <si>
-    <t>Ведомости / РЖД</t>
-  </si>
-  <si>
-    <t>https://www.vedomosti.ru/investments/news/2026/03/26/1185822-pribil-rzhd?from=newsline_partner</t>
-  </si>
-  <si>
-    <t>стратегические клиенты, ИТ-проекты</t>
-  </si>
-  <si>
-    <t>ухудшение финансового результата -&gt; давление на инвестпрограмму и проекты -&gt; более осторожный клиентский спрос</t>
-  </si>
-  <si>
-    <t>Добавлено в клиентский контур как стратегический сигнал</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>В течение Q1 2026 тарифная и торговая неопределенность усиливала внешний фон осторожности для бизнеса.</t>
-  </si>
-  <si>
-    <t>торговые риски -&gt; осторожность компаний -&gt; более жесткие бюджеты и найм</t>
-  </si>
-  <si>
-    <t>Использовано в квартальном внешнем контуре</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>Глобальный техсектор в Q1 2026 продолжал ужесточать требования к эффективности и фильтровать роли на фоне инвестиций в ИИ.</t>
-  </si>
-  <si>
-    <t>давление на эффективность -&gt; сокращения и жесткий отбор ролей -&gt; охлаждение внешнего ИТ-контура</t>
-  </si>
-  <si>
-    <t>Использовано как внешний ИТ-сигнал квартала</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>На входе в 2026 год усиливалась связка между ИИ, навыками и ростом порога входа на часть ролей.</t>
-  </si>
-  <si>
-    <t>рост ИИ и автоматизации -&gt; повышение требований к навыкам -&gt; более избирательный найм</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>Сигналы по финансовому ухудшению РЖД усиливали риск более осторожного клиентского спроса на проекты и подряд.</t>
-  </si>
-  <si>
-    <t>ухудшение финансового результата -&gt; давление на инвестиции и проекты -&gt; более осторожный спрос клиента</t>
-  </si>
-  <si>
-    <t>Использовано в контуре стратегических компаний</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>Российский рынок труда</t>
-  </si>
-  <si>
-    <t>Доля компаний с кадровым дефицитом снизилась с 65% до 51%; компании стали осторожнее и выборочнее в найме.</t>
-  </si>
-  <si>
-    <t>Комерсант</t>
-  </si>
-  <si>
-    <t>https://www.kommersant.ru/doc/8590343</t>
-  </si>
-  <si>
-    <t>рынок труда, значимые работодатели</t>
-  </si>
-  <si>
-    <t>Ослабление дефицита кадров усиливает позицию работодателя и снижает готовность нанимать впрок.</t>
-  </si>
-  <si>
-    <t>апрельский месячный выпуск</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>ИИ и труд</t>
-  </si>
-  <si>
-    <t>ИИ может высвободить до 30% рабочего времени к 2030 году; тема автоматизации напрямую связана с перераспределением задач и ростом требований к ролям.</t>
-  </si>
-  <si>
-    <t>РБК</t>
-  </si>
-  <si>
-    <t>https://tv.rbc.ru/archive/industries_spb/69e250b62ae5962fee09ed59</t>
-  </si>
-  <si>
-    <t>Автоматизация части рутинных задач усиливает спрос на прикладную эффективность и давит на нижний вход в профессию.</t>
   </si>
 </sst>
 </file>
@@ -808,9 +603,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" ns3:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.7265625" bestFit="1" customWidth="1"/>
@@ -822,7 +617,7 @@
     <col min="8" max="8" width="24.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="1" customFormat="1" ns3:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -848,7 +643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ns3:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -874,7 +669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ns3:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -900,7 +695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ns3:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -926,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ns3:dyDescent="0.35">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -952,7 +747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ns3:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -978,7 +773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ns3:dyDescent="0.35">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1004,7 +799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ns3:dyDescent="0.35">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1030,7 +825,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ns3:dyDescent="0.35">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1056,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ns3:dyDescent="0.35">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1082,7 +877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ns3:dyDescent="0.35">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -1108,7 +903,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ns3:dyDescent="0.35">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -1135,28 +930,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H12" ns2:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" ns4:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20386"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411787B5-993E-4BC3-A4CF-943B4FA2DEF4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Справочник_типов_событий" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
 </file>